--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-06 13:21</t>
+          <t>更新时间: 2026-09-07 13:30</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-07 13:30</t>
+          <t>更新时间: 2026-09-08 13:29</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-08 13:29</t>
+          <t>更新时间: 2026-09-09 13:36</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-09 13:36</t>
+          <t>更新时间: 2026-09-10 13:27</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-10 13:27</t>
+          <t>更新时间: 2026-09-11 13:28</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-11 13:28</t>
+          <t>更新时间: 2026-09-12 13:17</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-12 13:17</t>
+          <t>更新时间: 2026-09-13 13:31</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-13 13:31</t>
+          <t>更新时间: 2026-09-14 13:35</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-14 13:35</t>
+          <t>更新时间: 2026-09-15 13:36</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-15 13:36</t>
+          <t>更新时间: 2026-09-16 13:31</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-16 13:31</t>
+          <t>更新时间: 2026-09-17 13:37</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-17 13:37</t>
+          <t>更新时间: 2026-09-18 13:25</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-18 13:25</t>
+          <t>更新时间: 2026-09-19 13:20</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-19 13:20</t>
+          <t>更新时间: 2026-09-20 13:34</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-20 13:34</t>
+          <t>更新时间: 2026-09-21 13:43</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-21 13:43</t>
+          <t>更新时间: 2026-09-22 13:40</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-22 13:40</t>
+          <t>更新时间: 2026-09-23 13:24</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-23 13:24</t>
+          <t>更新时间: 2026-09-24 13:41</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-24 13:41</t>
+          <t>更新时间: 2026-09-24 16:04</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-24 16:04</t>
+          <t>更新时间: 2026-09-24 16:24</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-24 16:24</t>
+          <t>更新时间: 2026-09-24 17:17</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-24 17:17</t>
+          <t>更新时间: 2026-09-24 23:54</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-24 23:54</t>
+          <t>更新时间: 2026-09-25 23:54</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-25 23:54</t>
+          <t>更新时间: 2026-09-26 23:05</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-26 23:05</t>
+          <t>更新时间: 2026-09-27 23:47</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-27 23:47</t>
+          <t>更新时间: 2026-09-29 02:42</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-29 02:42</t>
+          <t>更新时间: 2026-09-30 00:59</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-30 00:59</t>
+          <t>更新时间: 2026-10-01 00:57</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-01 00:57</t>
+          <t>更新时间: 2026-10-02 01:29</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-02 01:29</t>
+          <t>更新时间: 2026-10-03 00:47</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-03 00:47</t>
+          <t>更新时间: 2026-10-03 23:12</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-03 23:12</t>
+          <t>更新时间: 2026-10-04 23:57</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-04 23:57</t>
+          <t>更新时间: 2026-10-06 03:51</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-06 03:51</t>
+          <t>更新时间: 2026-10-07 01:23</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-07 01:23</t>
+          <t>更新时间: 2026-10-08 01:56</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-08 01:56</t>
+          <t>更新时间: 2026-10-09 01:58</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-09 01:58</t>
+          <t>更新时间: 2026-10-10 01:31</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-10 01:31</t>
+          <t>更新时间: 2026-10-11 00:20</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-11 00:20</t>
+          <t>更新时间: 2026-10-12 00:43</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-12 00:43</t>
+          <t>更新时间: 2026-10-13 04:24</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-13 04:24</t>
+          <t>更新时间: 2026-10-14 02:27</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-14 02:27</t>
+          <t>更新时间: 2026-10-14 23:56</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-14 23:56</t>
+          <t>更新时间: 2026-10-15 23:44</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-15 23:44</t>
+          <t>更新时间: 2026-10-16 23:28</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-16 23:28</t>
+          <t>更新时间: 2026-10-17 22:20</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-17 22:20</t>
+          <t>更新时间: 2026-10-18 22:45</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-18 22:45</t>
+          <t>更新时间: 2026-10-20 01:40</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-20 01:40</t>
+          <t>更新时间: 2026-10-20 23:48</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-20 23:48</t>
+          <t>更新时间: 2026-10-22 00:04</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-22 00:04</t>
+          <t>更新时间: 2026-10-22 23:59</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-22 23:59</t>
+          <t>更新时间: 2026-10-23 23:51</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-23 23:51</t>
+          <t>更新时间: 2026-10-24 22:46</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-24 22:46</t>
+          <t>更新时间: 2026-10-25 23:01</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-25 23:01</t>
+          <t>更新时间: 2026-10-27 01:33</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-27 01:33</t>
+          <t>更新时间: 2026-10-28 00:49</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-28 00:49</t>
+          <t>更新时间: 2026-10-29 01:17</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-29 01:17</t>
+          <t>更新时间: 2026-10-30 01:30</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-30 01:30</t>
+          <t>更新时间: 2026-10-31 01:07</t>
         </is>
       </c>
     </row>
